--- a/output/rebalance_day_2026-03-25_185648_strategy1/rebalance_day_report.xlsx
+++ b/output/rebalance_day_2026-03-25_185648_strategy1/rebalance_day_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\rebalance_day_2026-03-25_185648\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\rebalance_day_2026-03-25_185648_strategy1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998B6A3A-35A4-4A6D-A907-A878BFE2C241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEBE713-A1AB-43AE-9502-E94A0B915DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14870" yWindow="5810" windowWidth="21600" windowHeight="11310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rebalance_Day_Status" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="223">
   <si>
     <t>Parameter</t>
   </si>
@@ -682,13 +682,29 @@
   <si>
     <t>MU:20.0%, SNDK:40.0%, WDC:40.0%</t>
   </si>
+  <si>
+    <t>SNDK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -728,7 +744,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2567,7 +2583,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>221</v>
       </c>
       <c r="F33">
         <v>0.39999999999999769</v>
@@ -2649,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="F35">
         <v>9.4824723323286431E-17</v>
@@ -2690,13 +2706,13 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="F36">
         <v>0.2000000000000004</v>
       </c>
       <c r="G36">
-        <v>426.1300048828125</v>
+        <v>426.13000488281199</v>
       </c>
       <c r="H36">
         <v>382.08999633789063</v>
@@ -3141,7 +3157,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>93</v>
+        <v>219</v>
       </c>
       <c r="F47">
         <v>0.39999999999999941</v>
